--- a/data/modelling/clustering/celulares/df_centroids_values.xlsx
+++ b/data/modelling/clustering/celulares/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Año de lanzamiento</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -461,147 +461,262 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Versión original del sistema operativo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución de la pantalla</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tecnología de la pantalla</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Píxeles por pulgada de la pantalla</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Frecuencia de actualización de la pantalla</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Brillo máximo de la pantalla</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Con pantalla táctil</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de batería</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Con carga rápida</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Con carga inalámbrica</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Con batería removible</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de conector de carga</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Con conector USB</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Con conector jack 3.5 mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Con Wi-Fi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Con Bluetooth</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Con NFC</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Es Dual SIM</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad de ranuras para tarjeta SIM</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaños de tarjeta SIM compatibles</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Memoria interna</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Con ranura para tarjeta de memoria</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Tipos de tarjeta de memoria</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>Resolución de la cámara trasera principal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Con cámara</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Características principales de las cámaras</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Cantidad de cámaras traseras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución de las cámaras traseras</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad de cámaras frontales</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución de video de la cámara frontal</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Zoom digital</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Con lector de huella digital</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Altura x Ancho x Profundidad</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Con reconocimiento facial</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Con reconocimiento de iris</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Con teclado QWERTY físico</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Modelo del procesador</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Con sensor de proximidad</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Es Dual SIM</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad de ranuras para tarjeta SIM</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Memoria interna</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Resolución de la pantalla</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Con teclado QWERTY físico</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Con conector USB</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Con Wi-Fi</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Con flash en la cámara frontal</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mejores en calidad</t>
+          <t>Buena relacion precio - calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75507.48558758314</v>
+        <v>74103.32487309644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -611,13 +726,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20E</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
+          <t>20 Pro</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2020.915151515152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -626,141 +739,254 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13 Mpx</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>6.5 "</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Full HD+</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1080 px x 2400 px</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DotDisplay</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>269 ppi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>90 Hz</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>450 cd/m²</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Polímero de litio</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>190 g</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4G/LTE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>USB-C</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.487046632124352</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>128 GB</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>4 GB</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>48 Mpx</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>1920 px x 1080 px</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>8 Mpx</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>2.57752808988764</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>165.64 mm x 75.59 mm x 8.8 mm</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Bokeh,Modo belleza,Foto HDR,Panorámica</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2.880829015544041</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>48 Mpx/2 Mpx/2 Mpx</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.005181347150259</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1920 px x 1080 px</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>MediaTek MTK6762D</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>7.518018018018018</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.408482142857143</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>128 GB</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>4 GB</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>6.5 "</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Full HD+</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1080 px x 2400 px</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>5000 mAh</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4G/LTE</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="BA2" t="n">
+        <v>7.875647668393782</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2 GHz</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Mejor relacion precio - calidad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8376.889999999999</v>
+        <v>72888.43269230769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -770,121 +996,125 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
+          <t>G60s</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2019.297872340426</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KaiOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.08 Mpx</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>320 px x 240 px</t>
+          <t>6.5 "</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.08 Mpx</t>
+          <t>Full HD+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1.018181818181818</v>
+          <t>1080 px x 2400 px</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>126.4 mm x 53 mm x 12 mm</t>
+          <t>395 ppi</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Spreadtrum SC6531E</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>1.375</v>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>625 cd/m²</t>
+        </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.847222222222222</v>
+          <t>5000 mAh</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Polímero de litio</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>32 MB</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>32 MB</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.4 "</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>QQVGA</t>
+          <t>189 g</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>128 px x 160 px</t>
+          <t>4G/LTE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>USB-C</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>800 mAh</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -894,7 +1124,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -902,7 +1132,114 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" t="n">
+        <v>1.288461538461539</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>128 GB</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>6 GB</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>12 Mpx</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>3840 px x 2160 px</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>8 Mpx</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Flash LED</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.754807692307693</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>12 Mpx/12 Mpx</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.087804878048781</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>1920 px x 1080 px</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>Snapdragon 720G</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.673076923076923</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2.3 GHz</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -911,77 +1248,79 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Caros y buena calidad</t>
+          <t>Baratos y calidad acorde</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>177480.9772727273</v>
+        <v>28038.57954545454</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iPhone SE (2nd Generation)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Azul Sierra</t>
-        </is>
+          <t>1 Plus</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2018.05</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>5 "</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>FWVGA+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>2.068181818181818</v>
+          <t>240 px x 320 px</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>RawColor display</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>138.4 mm x 67.3 mm x 7.3 mm</t>
+          <t>167 ppi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apple A15 Bionic</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>5.75</v>
+          <t>120 Hz</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>600 cd/m²</t>
+        </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -990,40 +1329,42 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.056818181818182</v>
+          <t>2000 mAh</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Ion de litio</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>128 GB</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>6.1 "</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>134 g</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>750 px x 1334 px</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Micro-USB</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1033,27 +1374,27 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1821 mAh</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4G/LTE</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1061,9 +1402,116 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="AG4" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>32 MB</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1 GB</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>5 Mpx</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1280 px x 720 px</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>5 Mpx</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Reconocimiento facial</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.217391304347826</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>16 Mpx/8 Mpx/2 Mpx/0.3 Mpx</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>1280 px x 720 px</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>MediaTek MT6739</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1.28 GHz</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1522,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54560.73809523809</v>
+        <v>67182.73333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,18 +1531,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Galaxy S</t>
+          <t>Galaxy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S21 FE 5G</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2018.483333333333</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1103,124 +1549,507 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>9.0 Pie</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5.5 "</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>HD+</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1080 px x 2340 px</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Infinity-V</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>403 ppi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>500 cd/m²</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3000 mAh</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Ion de litio</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>155 g</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4G/LTE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>USB-C</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.184049079754601</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>32 GB</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>4 GB</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>13 Mpx</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>1920 px x 1080 px</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>5 Mpx</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1280 px x 720 px</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>5 Mpx</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.671052631578947</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>137.6 mm x 65.7 mm x 9.9 mm</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>MediaTek MT6739</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>5.82051282051282</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1.23943661971831</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>16 GB</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1 GB</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>5 "</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Full HD+</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>480 px x 960 px</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2000 mAh</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4G/LTE</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Flash LED,Autofocus</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.729559748427673</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>16 Mpx/5 Mpx</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.073619631901841</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>1920 px x 1080 px</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>8x</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>Exynos 7870</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1.6 GHz</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Calidad a alto costo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>232821.9629629629</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>iPhone</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>iPhone 13 Pro</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2019.573333333333</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6.1 "</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1170 px x 2532 px</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Super Retina XDR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>326 ppi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>120 Hz</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1200 cd/m²</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1821 mAh</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Ion de litio</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>203 g</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.012345679012346</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>128 GB</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>4 GB</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>12 Mpx</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>3840 px x 2160 px</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>12 Mpx</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Geoetiquetado,Modo noche,Modo ráfaga,Modo retrato,Panorama</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>12 Mpx/12 Mpx</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>3840 px x 2160 px</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>5x</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Apple A15 Bionic</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.851851851851852</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2.65 GHz</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/data/modelling/clustering/celulares/df_centroids_values.xlsx
+++ b/data/modelling/clustering/celulares/df_centroids_values.xlsx
@@ -708,15 +708,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Buena relacion precio - calidad</t>
+          <t>Escalon abajo de numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74103.32487309644</v>
+        <v>72356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2020.915151515152</v>
+        <v>2021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1080 px x 2400 px</t>
+          <t>720 px x 1600 px</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DotDisplay</t>
+          <t>Max Vision</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>90 Hz</t>
+          <t>60 Hz</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>450 cd/m²</t>
+          <t>400 cd/m²</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.487046632124352</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>2.880829015544041</v>
+        <v>3</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="AS2" t="n">
-        <v>1.005181347150259</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>7.875647668393782</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -978,29 +978,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Mejor relacion precio - calidad</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72888.43269230769</v>
+        <v>15384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Alcatel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>G60s</t>
+          <t>1 Plus</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2019.297872340426</v>
+        <v>2018</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1014,42 +1014,42 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.5 "</t>
+          <t>5 "</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Full HD+</t>
+          <t>FWVGA+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1080 px x 2400 px</t>
+          <t>480 px x 960 px</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Super AMOLED</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Retina</t>
+          <t>RawColor display</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>395 ppi</t>
+          <t>167 ppi</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>60 Hz</t>
+          <t>120 Hz</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>625 cd/m²</t>
+          <t>600 cd/m²</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>5000 mAh</t>
+          <t>2000 mAh</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Polímero de litio</t>
+          <t>Ion de litio</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1079,22 +1079,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>189 g</t>
+          <t>134 g</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4G/LTE</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>USB-C</t>
+          <t>Micro-USB</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1124,16 +1124,16 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.288461538461539</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>128 GB</t>
+          <t>32 MB</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6 GB</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1162,53 +1162,53 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>5 Mpx</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>8 Mpx</t>
+          <t>2 Mpx</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Flash LED</t>
+          <t>Reconocimiento facial</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2.754807692307693</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>12 Mpx/12 Mpx</t>
+          <t>8 Mpx/2 Mpx</t>
         </is>
       </c>
       <c r="AS3" t="n">
-        <v>1.087804878048781</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1223,15 +1223,15 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Snapdragon 720G</t>
+          <t>MediaTek MT6739</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>7.673076923076923</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2.3 GHz</t>
+          <t>1.3 GHz</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1241,36 +1241,36 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad acorde</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28038.57954545454</v>
+        <v>69024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Galaxy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1 Plus</t>
+          <t>Note 10 Pro (Global)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2018.05</v>
+        <v>2021</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1284,42 +1284,42 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5 "</t>
+          <t>6.67 "</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FWVGA+</t>
+          <t>Full HD+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>240 px x 320 px</t>
+          <t>1080 px x 2400 px</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>Super AMOLED</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RawColor display</t>
+          <t>DotDisplay</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>167 ppi</t>
+          <t>395 ppi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>120 Hz</t>
+          <t>60 Hz</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>600 cd/m²</t>
+          <t>625 cd/m²</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2000 mAh</t>
+          <t>5000 mAh</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Ion de litio</t>
+          <t>Polímero de litio</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1344,27 +1344,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>134 g</t>
+          <t>189 g</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>4G/LTE</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Micro-USB</t>
+          <t>USB-C</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1394,16 +1394,16 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>32 MB</t>
+          <t>128 GB</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>6 GB</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1432,30 +1432,30 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5 Mpx</t>
+          <t>64 Mpx</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>5 Mpx</t>
+          <t>8 Mpx</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Reconocimiento facial</t>
+          <t>Flash LED</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>1.217391304347826</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>16 Mpx/8 Mpx/2 Mpx/0.3 Mpx</t>
+          <t>12 Mpx/12 Mpx</t>
         </is>
       </c>
       <c r="AS4" t="n">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1493,15 +1493,15 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>MediaTek MT6739</t>
+          <t>Snapdragon 720G</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1.28 GHz</t>
+          <t>2.3 GHz</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1511,18 +1511,18 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero buenos</t>
+          <t>Baratos y calidad media</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67182.73333333334</v>
+        <v>71477</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2018.483333333333</v>
+        <v>2020</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.0 Pie</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1080 px x 2340 px</t>
+          <t>720 px x 1440 px</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>403 ppi</t>
+          <t>293 ppi</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.184049079754601</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1717,11 +1717,11 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Flash LED,Autofocus</t>
+          <t>Flash LED</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>1.729559748427673</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="AS5" t="n">
-        <v>1.073619631901841</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1781,18 +1781,18 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Calidad a alto costo</t>
+          <t>Caros y calidad media</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232821.9629629629</v>
+        <v>237198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2019.573333333333</v>
+        <v>2021</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.012345679012346</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1965,11 +1965,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>MicroSD</t>
-        </is>
-      </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
           <t>12 Mpx</t>
@@ -1991,7 +1987,7 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>2.111111111111111</v>
+        <v>2</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
@@ -2037,7 +2033,7 @@
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>5.851851851851852</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>

--- a/data/modelling/clustering/celulares/df_centroids_values.xlsx
+++ b/data/modelling/clustering/celulares/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD6"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,24 +699,19 @@
           <t>Con flash en la cámara frontal</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Escalon abajo de numero 1</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72356</v>
+        <v>79068</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -726,7 +721,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20 Pro</t>
+          <t>20 SE</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -754,7 +749,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>720 px x 1600 px</t>
+          <t>1080 px x 2400 px</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Max Vision</t>
+          <t>DotDisplay</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -779,7 +774,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400 cd/m²</t>
+          <t>450 cd/m²</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -859,11 +854,11 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -907,11 +902,11 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Bokeh,Modo belleza,Foto HDR,Panorámica</t>
+          <t>Belleza IA,Modo noche,Foto HDR,Flash LED</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
@@ -928,7 +923,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -965,11 +960,6 @@
         </is>
       </c>
       <c r="BC2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -978,15 +968,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Totalmente basicos</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15384</v>
+        <v>17369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alcatel</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1000,7 +990,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1014,7 +1004,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5 "</t>
+          <t>2.4 "</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1024,7 +1014,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>480 px x 960 px</t>
+          <t>128 px x 160 px</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1047,19 +1037,15 @@
           <t>120 Hz</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>600 cd/m²</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2000 mAh</t>
+          <t>800 mAh</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1069,7 +1055,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1137,7 +1123,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Nano-SIM</t>
+          <t>Mini-SIM</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1231,15 +1217,10 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1.3 GHz</t>
+          <t>1.28 GHz</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1248,11 +1229,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Baratos y calidad alta</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69024</v>
+        <v>40983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1266,11 +1247,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Note 10 Pro (Global)</t>
+          <t>Galaxy S8 Plus</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1279,12 +1260,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7.0 Nougat</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.67 "</t>
+          <t>6.2 "</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1294,7 +1275,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1080 px x 2400 px</t>
+          <t>1440 px x 2960 px</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1304,12 +1285,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DotDisplay</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>395 ppi</t>
+          <t>531 ppi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1329,12 +1310,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>5000 mAh</t>
+          <t>3000 mAh</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Polímero de litio</t>
+          <t>Ion de litio</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1354,7 +1335,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>189 g</t>
+          <t>155 g</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1412,12 +1393,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>128 GB</t>
+          <t>16 GB</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6 GB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1432,7 +1413,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>64 Mpx</t>
+          <t>12 Mpx</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1442,7 +1423,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>8 Mpx</t>
+          <t>5 Mpx</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1451,7 +1432,7 @@
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
@@ -1493,7 +1474,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Snapdragon 720G</t>
+          <t>Snapdragon 835</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1501,85 +1482,80 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2.3 GHz</t>
+          <t>1.4 GHz</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad media</t>
+          <t>Caros y calidad media</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71477</v>
+        <v>171452</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>iPhone 8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.5 "</t>
+          <t>6.1 "</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HD+</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>720 px x 1440 px</t>
+          <t>750 px x 1334 px</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Super AMOLED</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Infinity-V</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>293 ppi</t>
+          <t>326 ppi</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1589,7 +1565,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>500 cd/m²</t>
+          <t>625 cd/m²</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1599,7 +1575,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3000 mAh</t>
+          <t>1821 mAh</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1624,7 +1600,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>155 g</t>
+          <t>148 g</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1634,17 +1610,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>USB-C</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1682,7 +1658,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>32 GB</t>
+          <t>64 GB</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1692,7 +1668,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1702,22 +1678,22 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>13 Mpx</t>
+          <t>12 Mpx</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>5 Mpx</t>
+          <t>7 Mpx</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Flash LED</t>
+          <t>Cámara nocturna</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -1725,7 +1701,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>16 Mpx/5 Mpx</t>
+          <t>12 Mpx/12 Mpx</t>
         </is>
       </c>
       <c r="AS5" t="n">
@@ -1738,7 +1714,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1763,68 +1739,63 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Exynos 7870</t>
+          <t>Apple A11 Bionic</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1.6 GHz</t>
+          <t>2.65 GHz</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad media</t>
+          <t>Baratos y calidad media</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>237198</v>
+        <v>48443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Galaxy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>iPhone 13 Pro</t>
+          <t>J7 Prime</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9.0 Pie</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.1 "</t>
+          <t>5 "</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1834,32 +1805,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1170 px x 2532 px</t>
+          <t>720 px x 1280 px</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>Super AMOLED</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Super Retina XDR</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>326 ppi</t>
+          <t>294 ppi</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>120 Hz</t>
+          <t>60 Hz</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1200 cd/m²</t>
+          <t>625 cd/m²</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1869,7 +1840,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1821 mAh</t>
+          <t>3000 mAh</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1894,27 +1865,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>203 g</t>
+          <t>155 g</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5G</t>
+          <t>4G/LTE</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>USB-C</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1952,7 +1923,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>128 GB</t>
+          <t>32 GB</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1962,36 +1933,40 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>MicroSD</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>13 Mpx</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>5 Mpx</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Geoetiquetado,Modo noche,Modo ráfaga,Modo retrato,Panorama</t>
+          <t>Flash LED</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>12 Mpx/12 Mpx</t>
+          <t>16 Mpx/5 Mpx</t>
         </is>
       </c>
       <c r="AS6" t="n">
@@ -1999,12 +1974,12 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2029,25 +2004,20 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>Apple A15 Bionic</t>
+          <t>Exynos 7870</t>
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2.65 GHz</t>
+          <t>2.3 GHz</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/data/modelling/clustering/celulares/df_centroids_values.xlsx
+++ b/data/modelling/clustering/celulares/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC6"/>
+  <dimension ref="A1:BC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79068</v>
+        <v>68209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20 SE</t>
+          <t>Galaxy S8 Plus</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>269 ppi</t>
+          <t>405 ppi</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>450 cd/m²</t>
+          <t>625 cd/m²</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -854,11 +854,11 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Belleza IA,Modo noche,Foto HDR,Flash LED</t>
+          <t>Flash LED</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>48 Mpx/2 Mpx/2 Mpx</t>
+          <t>12 Mpx/12 Mpx</t>
         </is>
       </c>
       <c r="AS2" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>MediaTek MTK6762D</t>
+          <t>Snapdragon 835</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -968,29 +968,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Totalmente basicos</t>
+          <t>Caros y calidad media</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17369</v>
+        <v>158468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iPro</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 Plus</t>
+          <t>iPhone SE (2nd Generation)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -999,37 +999,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.4 "</t>
+          <t>6.1 "</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FWVGA+</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>128 px x 160 px</t>
+          <t>1080 px x 1920 px</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RawColor display</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>167 ppi</t>
+          <t>326 ppi</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1037,15 +1037,19 @@
           <t>120 Hz</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>625 cd/m²</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>800 mAh</t>
+          <t>4500 mAh</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1060,27 +1064,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>134 g</t>
+          <t>148 g</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>4G/LTE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Micro-USB</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1110,35 +1114,35 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Mini-SIM</t>
+          <t>Nano-SIM</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>32 MB</t>
+          <t>128 GB</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1148,22 +1152,22 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5 Mpx</t>
+          <t>12 Mpx</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 Mpx</t>
+          <t>7 Mpx</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Reconocimiento facial</t>
+          <t>Cámara nocturna</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>8 Mpx/2 Mpx</t>
+          <t>12 Mpx/12 Mpx</t>
         </is>
       </c>
       <c r="AS3" t="n">
@@ -1179,22 +1183,22 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1209,15 +1213,15 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>MediaTek MT6739</t>
+          <t>Apple A13 Bionic</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1.28 GHz</t>
+          <t>2.2 GHz</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1229,11 +1233,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad alta</t>
+          <t>Baratos y calidad media</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40983</v>
+        <v>42366</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1247,11 +1251,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galaxy S8 Plus</t>
+          <t>J7 Prime</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1260,17 +1264,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.0 Nougat</t>
+          <t>9.0 Pie</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.2 "</t>
+          <t>5.5 "</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Full HD+</t>
+          <t>HD+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1285,12 +1289,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Retina</t>
+          <t>Full Display</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>531 ppi</t>
+          <t>570 ppi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1393,7 +1397,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>16 GB</t>
+          <t>32 GB</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1413,12 +1417,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>13 Mpx</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1449,7 +1453,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Snapdragon 835</t>
+          <t>Exynos 7870</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1.4 GHz</t>
+          <t>1.6 GHz</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1494,33 +1498,33 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad media</t>
+          <t>Muy baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171452</v>
+        <v>11875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>iPhone 8</t>
+          <t>1 Plus</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1530,32 +1534,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.1 "</t>
+          <t>2.4 "</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>FWVGA+</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>750 px x 1334 px</t>
+          <t>128 px x 160 px</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Retina</t>
+          <t>RawColor display</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>326 ppi</t>
+          <t>167 ppi</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1565,17 +1569,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>625 cd/m²</t>
+          <t>500 cd/m²</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1821 mAh</t>
+          <t>800 mAh</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1585,42 +1589,42 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>148 g</t>
+          <t>134 g</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4G/LTE</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Micro-USB</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1640,35 +1644,35 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Nano-SIM</t>
+          <t>Mini-SIM</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>64 GB</t>
+          <t>32 MB</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1678,22 +1682,22 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>0.3 Mpx</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>7 Mpx</t>
+          <t>2 Mpx</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Cámara nocturna</t>
+          <t>Reconocimiento facial</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12 Mpx/12 Mpx</t>
+          <t>3 Mpx</t>
         </is>
       </c>
       <c r="AS5" t="n">
@@ -1709,22 +1713,22 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1739,283 +1743,18 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>Apple A11 Bionic</t>
+          <t>MediaTek MT6739</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2.65 GHz</t>
+          <t>1.3 GHz</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Baratos y calidad media</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>48443</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Galaxy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>J7 Prime</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>9.0 Pie</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5 "</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>720 px x 1280 px</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Super AMOLED</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Retina</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>294 ppi</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>60 Hz</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>625 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>3000 mAh</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Ion de litio</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>155 g</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4G/LTE</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>USB-C</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Nano-SIM</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>32 GB</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>4 GB</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>MicroSD</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>13 Mpx</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1920 px x 1080 px</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>5 Mpx</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Flash LED</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>16 Mpx/5 Mpx</t>
-        </is>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>1920 px x 1080 px</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>8x</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>Exynos 7870</t>
-        </is>
-      </c>
-      <c r="BA6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>2.3 GHz</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/modelling/clustering/celulares/df_centroids_values.xlsx
+++ b/data/modelling/clustering/celulares/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC5"/>
+  <dimension ref="A1:BD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,11 @@
           <t>Con flash en la cámara frontal</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -707,7 +712,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68209</v>
+        <v>76963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -721,7 +726,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Galaxy S8 Plus</t>
+          <t>A52</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -809,7 +814,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>190 g</t>
+          <t>189 g</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -948,7 +953,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Snapdragon 835</t>
+          <t>Snapdragon 720G</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -962,35 +967,40 @@
       <c r="BC2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad media</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>158468</v>
+        <v>16892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Lumia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>iPhone SE (2nd Generation)</t>
+          <t>A6 Mini</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -999,37 +1009,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.1 "</t>
+          <t>2.4 "</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>FWVGA+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1080 px x 1920 px</t>
+          <t>128 px x 160 px</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Retina</t>
+          <t>Full Display</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>326 ppi</t>
+          <t>167 ppi</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1039,17 +1049,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>625 cd/m²</t>
+          <t>500 cd/m²</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>4500 mAh</t>
+          <t>800 mAh</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1059,32 +1069,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>148 g</t>
+          <t>134 g</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4G/LTE</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Micro-USB</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1094,7 +1104,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1114,16 +1124,16 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1132,17 +1142,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>128 GB</t>
+          <t>32 MB</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1152,22 +1162,22 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12 Mpx</t>
+          <t>8 Mpx</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>7 Mpx</t>
+          <t>5 Mpx</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Cámara nocturna</t>
+          <t>Reconocimiento facial</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -1175,7 +1185,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>12 Mpx/12 Mpx</t>
+          <t>13 Mpx/2 Mpx</t>
         </is>
       </c>
       <c r="AS3" t="n">
@@ -1183,22 +1193,22 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1213,18 +1223,23 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Apple A13 Bionic</t>
+          <t>MediaTek MT6739</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2.2 GHz</t>
+          <t>1.3 GHz</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1233,11 +1248,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad media</t>
+          <t>Escalon debajo de numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42366</v>
+        <v>97316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1246,16 +1261,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>J7 Prime</t>
+          <t>iPhone SE (2nd Generation)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1264,7 +1279,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.0 Pie</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1279,22 +1294,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1440 px x 2960 px</t>
+          <t>720 px x 1600 px</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Super AMOLED</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Full Display</t>
+          <t>Super Retina XDR</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>570 ppi</t>
+          <t>326 ppi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>155 g</t>
+          <t>194 g</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1397,7 +1412,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>32 GB</t>
+          <t>64 GB</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>13 Mpx</t>
+          <t>12 Mpx</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1453,7 +1468,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1478,7 +1493,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Exynos 7870</t>
+          <t>Apple A15 Bionic</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1.6 GHz</t>
+          <t>1.8 GHz</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1494,269 +1509,9 @@
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Muy baratos pero calidad acorde</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>11875</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>iPro</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1 Plus</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2.4 "</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FWVGA+</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>128 px x 160 px</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>TFT</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>RawColor display</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>167 ppi</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>60 Hz</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>500 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>800 mAh</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Ion de litio</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>134 g</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2G</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Micro-USB</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Mini-SIM</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>32 MB</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1 GB</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>MicroSD</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0.3 Mpx</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>1280 px x 720 px</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2 Mpx</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Reconocimiento facial</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>3 Mpx</t>
-        </is>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>1280 px x 720 px</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>4x</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>MediaTek MT6739</t>
-        </is>
-      </c>
-      <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>1.3 GHz</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
